--- a/MiniTemplate/Datas/buffConfig.xlsx
+++ b/MiniTemplate/Datas/buffConfig.xlsx
@@ -5,12 +5,12 @@
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\Unity Project\TimeChip\TimeChip\MiniTemplate\Datas\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\UGit\TimeChip\MiniTemplate\Datas\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{2E6C8C74-E826-46AB-8ECA-0A42291793A6}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{24E18F92-26E9-4C5E-9932-3139BAE2A891}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-108" yWindow="-108" windowWidth="30936" windowHeight="16776" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -20,7 +20,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="78" uniqueCount="51">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="198" uniqueCount="99">
   <si>
     <t>##var</t>
   </si>
@@ -181,6 +181,150 @@
   <si>
     <t>int</t>
     <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>extraEffectType</t>
+  </si>
+  <si>
+    <t>extraEffectValue</t>
+  </si>
+  <si>
+    <t>附加效果类型；无附加效果时留空</t>
+  </si>
+  <si>
+    <t>附加效果数值；无附加效果时填 0</t>
+  </si>
+  <si>
+    <t>学习经验 I</t>
+  </si>
+  <si>
+    <t>学习经验 +8%</t>
+  </si>
+  <si>
+    <t>Replace</t>
+  </si>
+  <si>
+    <t>LearningExperienceMultiplier</t>
+  </si>
+  <si>
+    <t>学习经验 II</t>
+  </si>
+  <si>
+    <t>学习经验 +16%</t>
+  </si>
+  <si>
+    <t>学习经验 III</t>
+  </si>
+  <si>
+    <t>学习经验 +25%</t>
+  </si>
+  <si>
+    <t>商店增益 I</t>
+  </si>
+  <si>
+    <t>商品价格 -3%</t>
+  </si>
+  <si>
+    <t>ShopPriceMultiplier</t>
+  </si>
+  <si>
+    <t>商店增益 II</t>
+  </si>
+  <si>
+    <t>商品价格 -6%</t>
+  </si>
+  <si>
+    <t>商店增益 III</t>
+  </si>
+  <si>
+    <t>商品价格 -10%</t>
+  </si>
+  <si>
+    <t>邻里机遇 I</t>
+  </si>
+  <si>
+    <t>正面机遇权重 ×1.12</t>
+  </si>
+  <si>
+    <t>PositiveEncounterWeightMultiplier</t>
+  </si>
+  <si>
+    <t>邻里机遇 II</t>
+  </si>
+  <si>
+    <t>正面机遇权重 ×1.25，机遇奖励 +5%</t>
+  </si>
+  <si>
+    <t>PositiveEncounterRewardMultiplier</t>
+  </si>
+  <si>
+    <t>邻里机遇 III</t>
+  </si>
+  <si>
+    <t>正面机遇权重 ×1.40，机遇奖励 +10%</t>
+  </si>
+  <si>
+    <t>零工收益 I</t>
+  </si>
+  <si>
+    <t>零工模拟币 +5%</t>
+  </si>
+  <si>
+    <t>零工收益 II</t>
+  </si>
+  <si>
+    <t>零工模拟币 +10%</t>
+  </si>
+  <si>
+    <t>零工收益 III</t>
+  </si>
+  <si>
+    <t>零工模拟币 +18%</t>
+  </si>
+  <si>
+    <t>健康增益 I</t>
+  </si>
+  <si>
+    <t>治疗及药物恢复量 +10%</t>
+  </si>
+  <si>
+    <t>TreatmentAndDrugEffectMultiplier</t>
+  </si>
+  <si>
+    <t>健康增益 II</t>
+  </si>
+  <si>
+    <t>治疗及药物恢复量 +20%，治疗费用 -5%</t>
+  </si>
+  <si>
+    <t>TreatmentCostMultiplier</t>
+  </si>
+  <si>
+    <t>健康增益 III</t>
+  </si>
+  <si>
+    <t>治疗及药物恢复量 +30%，治疗费用 -10%</t>
+  </si>
+  <si>
+    <t>抽奖概率 I</t>
+  </si>
+  <si>
+    <t>稀有奖励权重 ×1.08</t>
+  </si>
+  <si>
+    <t>RareLotteryRewardWeightMultiplier</t>
+  </si>
+  <si>
+    <t>抽奖概率 II</t>
+  </si>
+  <si>
+    <t>稀有奖励权重 ×1.16</t>
+  </si>
+  <si>
+    <t>抽奖概率 III</t>
+  </si>
+  <si>
+    <t>稀有奖励权重 ×1.28</t>
   </si>
 </sst>
 </file>
@@ -551,25 +695,28 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:O7"/>
-  <sheetFormatPr defaultRowHeight="13.5" x14ac:dyDescent="0.15"/>
+  <dimension ref="A1:Q25"/>
+  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="1" max="3" width="12" customWidth="1"/>
-    <col min="4" max="4" width="43.75" customWidth="1"/>
-    <col min="5" max="5" width="37.5" customWidth="1"/>
-    <col min="6" max="6" width="33" customWidth="1"/>
-    <col min="7" max="7" width="18" customWidth="1"/>
-    <col min="8" max="8" width="38" customWidth="1"/>
-    <col min="9" max="9" width="29" customWidth="1"/>
-    <col min="10" max="10" width="22.25" customWidth="1"/>
-    <col min="11" max="11" width="12" customWidth="1"/>
-    <col min="12" max="12" width="47" customWidth="1"/>
-    <col min="13" max="13" width="24.25" customWidth="1"/>
-    <col min="14" max="14" width="121.125" customWidth="1"/>
-    <col min="15" max="15" width="34.25" customWidth="1"/>
+    <col min="1" max="2" width="8.5546875" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="13.88671875" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="44.6640625" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="9.5546875" bestFit="1" customWidth="1"/>
+    <col min="6" max="6" width="40.21875" bestFit="1" customWidth="1"/>
+    <col min="7" max="7" width="24.88671875" bestFit="1" customWidth="1"/>
+    <col min="8" max="8" width="47.88671875" bestFit="1" customWidth="1"/>
+    <col min="9" max="9" width="30.33203125" bestFit="1" customWidth="1"/>
+    <col min="10" max="10" width="22.6640625" bestFit="1" customWidth="1"/>
+    <col min="11" max="11" width="10.5546875" bestFit="1" customWidth="1"/>
+    <col min="12" max="12" width="50.109375" bestFit="1" customWidth="1"/>
+    <col min="13" max="13" width="20.44140625" bestFit="1" customWidth="1"/>
+    <col min="14" max="14" width="131.33203125" bestFit="1" customWidth="1"/>
+    <col min="15" max="15" width="39.109375" bestFit="1" customWidth="1"/>
+    <col min="16" max="16" width="36.88671875" bestFit="1" customWidth="1"/>
+    <col min="17" max="17" width="33.6640625" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:15" x14ac:dyDescent="0.15">
+    <row r="1" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
@@ -615,8 +762,14 @@
       <c r="O1" s="1" t="s">
         <v>14</v>
       </c>
-    </row>
-    <row r="2" spans="1:15" x14ac:dyDescent="0.15">
+      <c r="P1" t="s">
+        <v>51</v>
+      </c>
+      <c r="Q1" t="s">
+        <v>52</v>
+      </c>
+    </row>
+    <row r="2" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A2" s="2" t="s">
         <v>15</v>
       </c>
@@ -662,8 +815,14 @@
       <c r="O2" s="2" t="s">
         <v>18</v>
       </c>
-    </row>
-    <row r="3" spans="1:15" x14ac:dyDescent="0.15">
+      <c r="P2" t="s">
+        <v>17</v>
+      </c>
+      <c r="Q2" t="s">
+        <v>18</v>
+      </c>
+    </row>
+    <row r="3" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A3" s="3" t="s">
         <v>19</v>
       </c>
@@ -709,8 +868,14 @@
       <c r="O3" s="3" t="s">
         <v>20</v>
       </c>
-    </row>
-    <row r="4" spans="1:15" x14ac:dyDescent="0.15">
+      <c r="P3" t="s">
+        <v>20</v>
+      </c>
+      <c r="Q3" t="s">
+        <v>20</v>
+      </c>
+    </row>
+    <row r="4" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A4" s="4" t="s">
         <v>21</v>
       </c>
@@ -756,8 +921,14 @@
       <c r="O4" s="4" t="s">
         <v>32</v>
       </c>
-    </row>
-    <row r="5" spans="1:15" x14ac:dyDescent="0.15">
+      <c r="P4" t="s">
+        <v>53</v>
+      </c>
+      <c r="Q4" t="s">
+        <v>54</v>
+      </c>
+    </row>
+    <row r="5" spans="1:17" x14ac:dyDescent="0.25">
       <c r="B5">
         <v>1001</v>
       </c>
@@ -798,7 +969,7 @@
         <v>0.2</v>
       </c>
     </row>
-    <row r="6" spans="1:15" x14ac:dyDescent="0.15">
+    <row r="6" spans="1:17" x14ac:dyDescent="0.25">
       <c r="B6">
         <v>1002</v>
       </c>
@@ -839,7 +1010,7 @@
         <v>-0.2</v>
       </c>
     </row>
-    <row r="7" spans="1:15" x14ac:dyDescent="0.15">
+    <row r="7" spans="1:17" x14ac:dyDescent="0.25">
       <c r="B7">
         <v>1003</v>
       </c>
@@ -878,6 +1049,810 @@
       </c>
       <c r="O7">
         <v>0.1</v>
+      </c>
+    </row>
+    <row r="8" spans="1:17" x14ac:dyDescent="0.25">
+      <c r="B8">
+        <v>2001</v>
+      </c>
+      <c r="C8" t="s">
+        <v>55</v>
+      </c>
+      <c r="D8" t="s">
+        <v>56</v>
+      </c>
+      <c r="E8">
+        <v>1000</v>
+      </c>
+      <c r="F8" t="s">
+        <v>34</v>
+      </c>
+      <c r="G8">
+        <v>0</v>
+      </c>
+      <c r="I8" t="s">
+        <v>42</v>
+      </c>
+      <c r="J8">
+        <v>0</v>
+      </c>
+      <c r="K8">
+        <v>1</v>
+      </c>
+      <c r="L8" t="s">
+        <v>57</v>
+      </c>
+      <c r="M8">
+        <v>0</v>
+      </c>
+      <c r="N8" t="s">
+        <v>58</v>
+      </c>
+      <c r="O8">
+        <v>0.08</v>
+      </c>
+      <c r="Q8">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="9" spans="1:17" x14ac:dyDescent="0.25">
+      <c r="B9">
+        <v>2002</v>
+      </c>
+      <c r="C9" t="s">
+        <v>59</v>
+      </c>
+      <c r="D9" t="s">
+        <v>60</v>
+      </c>
+      <c r="E9">
+        <v>1000</v>
+      </c>
+      <c r="F9" t="s">
+        <v>34</v>
+      </c>
+      <c r="G9">
+        <v>0</v>
+      </c>
+      <c r="I9" t="s">
+        <v>42</v>
+      </c>
+      <c r="J9">
+        <v>0</v>
+      </c>
+      <c r="K9">
+        <v>1</v>
+      </c>
+      <c r="L9" t="s">
+        <v>57</v>
+      </c>
+      <c r="M9">
+        <v>0</v>
+      </c>
+      <c r="N9" t="s">
+        <v>58</v>
+      </c>
+      <c r="O9">
+        <v>0.16</v>
+      </c>
+      <c r="Q9">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="10" spans="1:17" x14ac:dyDescent="0.25">
+      <c r="B10">
+        <v>2003</v>
+      </c>
+      <c r="C10" t="s">
+        <v>61</v>
+      </c>
+      <c r="D10" t="s">
+        <v>62</v>
+      </c>
+      <c r="E10">
+        <v>1000</v>
+      </c>
+      <c r="F10" t="s">
+        <v>34</v>
+      </c>
+      <c r="G10">
+        <v>0</v>
+      </c>
+      <c r="I10" t="s">
+        <v>42</v>
+      </c>
+      <c r="J10">
+        <v>0</v>
+      </c>
+      <c r="K10">
+        <v>1</v>
+      </c>
+      <c r="L10" t="s">
+        <v>57</v>
+      </c>
+      <c r="M10">
+        <v>0</v>
+      </c>
+      <c r="N10" t="s">
+        <v>58</v>
+      </c>
+      <c r="O10">
+        <v>0.25</v>
+      </c>
+      <c r="Q10">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="11" spans="1:17" x14ac:dyDescent="0.25">
+      <c r="B11">
+        <v>2004</v>
+      </c>
+      <c r="C11" t="s">
+        <v>63</v>
+      </c>
+      <c r="D11" t="s">
+        <v>64</v>
+      </c>
+      <c r="E11">
+        <v>1000</v>
+      </c>
+      <c r="F11" t="s">
+        <v>34</v>
+      </c>
+      <c r="G11">
+        <v>0</v>
+      </c>
+      <c r="I11" t="s">
+        <v>42</v>
+      </c>
+      <c r="J11">
+        <v>0</v>
+      </c>
+      <c r="K11">
+        <v>1</v>
+      </c>
+      <c r="L11" t="s">
+        <v>57</v>
+      </c>
+      <c r="M11">
+        <v>0</v>
+      </c>
+      <c r="N11" t="s">
+        <v>65</v>
+      </c>
+      <c r="O11">
+        <v>-0.03</v>
+      </c>
+      <c r="Q11">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="12" spans="1:17" x14ac:dyDescent="0.25">
+      <c r="B12">
+        <v>2005</v>
+      </c>
+      <c r="C12" t="s">
+        <v>66</v>
+      </c>
+      <c r="D12" t="s">
+        <v>67</v>
+      </c>
+      <c r="E12">
+        <v>1000</v>
+      </c>
+      <c r="F12" t="s">
+        <v>34</v>
+      </c>
+      <c r="G12">
+        <v>0</v>
+      </c>
+      <c r="I12" t="s">
+        <v>42</v>
+      </c>
+      <c r="J12">
+        <v>0</v>
+      </c>
+      <c r="K12">
+        <v>1</v>
+      </c>
+      <c r="L12" t="s">
+        <v>57</v>
+      </c>
+      <c r="M12">
+        <v>0</v>
+      </c>
+      <c r="N12" t="s">
+        <v>65</v>
+      </c>
+      <c r="O12">
+        <v>-0.06</v>
+      </c>
+      <c r="Q12">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="13" spans="1:17" x14ac:dyDescent="0.25">
+      <c r="B13">
+        <v>2006</v>
+      </c>
+      <c r="C13" t="s">
+        <v>68</v>
+      </c>
+      <c r="D13" t="s">
+        <v>69</v>
+      </c>
+      <c r="E13">
+        <v>1000</v>
+      </c>
+      <c r="F13" t="s">
+        <v>34</v>
+      </c>
+      <c r="G13">
+        <v>0</v>
+      </c>
+      <c r="I13" t="s">
+        <v>42</v>
+      </c>
+      <c r="J13">
+        <v>0</v>
+      </c>
+      <c r="K13">
+        <v>1</v>
+      </c>
+      <c r="L13" t="s">
+        <v>57</v>
+      </c>
+      <c r="M13">
+        <v>0</v>
+      </c>
+      <c r="N13" t="s">
+        <v>65</v>
+      </c>
+      <c r="O13">
+        <v>-0.1</v>
+      </c>
+      <c r="Q13">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="14" spans="1:17" x14ac:dyDescent="0.25">
+      <c r="B14">
+        <v>2007</v>
+      </c>
+      <c r="C14" t="s">
+        <v>70</v>
+      </c>
+      <c r="D14" t="s">
+        <v>71</v>
+      </c>
+      <c r="E14">
+        <v>1000</v>
+      </c>
+      <c r="F14" t="s">
+        <v>34</v>
+      </c>
+      <c r="G14">
+        <v>0</v>
+      </c>
+      <c r="I14" t="s">
+        <v>42</v>
+      </c>
+      <c r="J14">
+        <v>0</v>
+      </c>
+      <c r="K14">
+        <v>1</v>
+      </c>
+      <c r="L14" t="s">
+        <v>57</v>
+      </c>
+      <c r="M14">
+        <v>0</v>
+      </c>
+      <c r="N14" t="s">
+        <v>72</v>
+      </c>
+      <c r="O14">
+        <v>0.12</v>
+      </c>
+      <c r="Q14">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="15" spans="1:17" x14ac:dyDescent="0.25">
+      <c r="B15">
+        <v>2008</v>
+      </c>
+      <c r="C15" t="s">
+        <v>73</v>
+      </c>
+      <c r="D15" t="s">
+        <v>74</v>
+      </c>
+      <c r="E15">
+        <v>1000</v>
+      </c>
+      <c r="F15" t="s">
+        <v>34</v>
+      </c>
+      <c r="G15">
+        <v>0</v>
+      </c>
+      <c r="I15" t="s">
+        <v>42</v>
+      </c>
+      <c r="J15">
+        <v>0</v>
+      </c>
+      <c r="K15">
+        <v>1</v>
+      </c>
+      <c r="L15" t="s">
+        <v>57</v>
+      </c>
+      <c r="M15">
+        <v>0</v>
+      </c>
+      <c r="N15" t="s">
+        <v>72</v>
+      </c>
+      <c r="O15">
+        <v>0.25</v>
+      </c>
+      <c r="P15" t="s">
+        <v>75</v>
+      </c>
+      <c r="Q15">
+        <v>0.05</v>
+      </c>
+    </row>
+    <row r="16" spans="1:17" x14ac:dyDescent="0.25">
+      <c r="B16">
+        <v>2009</v>
+      </c>
+      <c r="C16" t="s">
+        <v>76</v>
+      </c>
+      <c r="D16" t="s">
+        <v>77</v>
+      </c>
+      <c r="E16">
+        <v>1000</v>
+      </c>
+      <c r="F16" t="s">
+        <v>34</v>
+      </c>
+      <c r="G16">
+        <v>0</v>
+      </c>
+      <c r="I16" t="s">
+        <v>42</v>
+      </c>
+      <c r="J16">
+        <v>0</v>
+      </c>
+      <c r="K16">
+        <v>1</v>
+      </c>
+      <c r="L16" t="s">
+        <v>57</v>
+      </c>
+      <c r="M16">
+        <v>0</v>
+      </c>
+      <c r="N16" t="s">
+        <v>72</v>
+      </c>
+      <c r="O16">
+        <v>0.4</v>
+      </c>
+      <c r="P16" t="s">
+        <v>75</v>
+      </c>
+      <c r="Q16">
+        <v>0.1</v>
+      </c>
+    </row>
+    <row r="17" spans="2:17" x14ac:dyDescent="0.25">
+      <c r="B17">
+        <v>2010</v>
+      </c>
+      <c r="C17" t="s">
+        <v>78</v>
+      </c>
+      <c r="D17" t="s">
+        <v>79</v>
+      </c>
+      <c r="E17">
+        <v>1000</v>
+      </c>
+      <c r="F17" t="s">
+        <v>34</v>
+      </c>
+      <c r="G17">
+        <v>0</v>
+      </c>
+      <c r="I17" t="s">
+        <v>42</v>
+      </c>
+      <c r="J17">
+        <v>0</v>
+      </c>
+      <c r="K17">
+        <v>1</v>
+      </c>
+      <c r="L17" t="s">
+        <v>57</v>
+      </c>
+      <c r="M17">
+        <v>0</v>
+      </c>
+      <c r="N17" t="s">
+        <v>37</v>
+      </c>
+      <c r="O17">
+        <v>0.05</v>
+      </c>
+      <c r="Q17">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="18" spans="2:17" x14ac:dyDescent="0.25">
+      <c r="B18">
+        <v>2011</v>
+      </c>
+      <c r="C18" t="s">
+        <v>80</v>
+      </c>
+      <c r="D18" t="s">
+        <v>81</v>
+      </c>
+      <c r="E18">
+        <v>1000</v>
+      </c>
+      <c r="F18" t="s">
+        <v>34</v>
+      </c>
+      <c r="G18">
+        <v>0</v>
+      </c>
+      <c r="I18" t="s">
+        <v>42</v>
+      </c>
+      <c r="J18">
+        <v>0</v>
+      </c>
+      <c r="K18">
+        <v>1</v>
+      </c>
+      <c r="L18" t="s">
+        <v>57</v>
+      </c>
+      <c r="M18">
+        <v>0</v>
+      </c>
+      <c r="N18" t="s">
+        <v>37</v>
+      </c>
+      <c r="O18">
+        <v>0.1</v>
+      </c>
+      <c r="Q18">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="19" spans="2:17" x14ac:dyDescent="0.25">
+      <c r="B19">
+        <v>2012</v>
+      </c>
+      <c r="C19" t="s">
+        <v>82</v>
+      </c>
+      <c r="D19" t="s">
+        <v>83</v>
+      </c>
+      <c r="E19">
+        <v>1000</v>
+      </c>
+      <c r="F19" t="s">
+        <v>34</v>
+      </c>
+      <c r="G19">
+        <v>0</v>
+      </c>
+      <c r="I19" t="s">
+        <v>42</v>
+      </c>
+      <c r="J19">
+        <v>0</v>
+      </c>
+      <c r="K19">
+        <v>1</v>
+      </c>
+      <c r="L19" t="s">
+        <v>57</v>
+      </c>
+      <c r="M19">
+        <v>0</v>
+      </c>
+      <c r="N19" t="s">
+        <v>37</v>
+      </c>
+      <c r="O19">
+        <v>0.18</v>
+      </c>
+      <c r="Q19">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="20" spans="2:17" x14ac:dyDescent="0.25">
+      <c r="B20">
+        <v>2013</v>
+      </c>
+      <c r="C20" t="s">
+        <v>84</v>
+      </c>
+      <c r="D20" t="s">
+        <v>85</v>
+      </c>
+      <c r="E20">
+        <v>1000</v>
+      </c>
+      <c r="F20" t="s">
+        <v>34</v>
+      </c>
+      <c r="G20">
+        <v>0</v>
+      </c>
+      <c r="I20" t="s">
+        <v>42</v>
+      </c>
+      <c r="J20">
+        <v>0</v>
+      </c>
+      <c r="K20">
+        <v>1</v>
+      </c>
+      <c r="L20" t="s">
+        <v>57</v>
+      </c>
+      <c r="M20">
+        <v>0</v>
+      </c>
+      <c r="N20" t="s">
+        <v>86</v>
+      </c>
+      <c r="O20">
+        <v>0.1</v>
+      </c>
+      <c r="Q20">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="21" spans="2:17" x14ac:dyDescent="0.25">
+      <c r="B21">
+        <v>2014</v>
+      </c>
+      <c r="C21" t="s">
+        <v>87</v>
+      </c>
+      <c r="D21" t="s">
+        <v>88</v>
+      </c>
+      <c r="E21">
+        <v>1000</v>
+      </c>
+      <c r="F21" t="s">
+        <v>34</v>
+      </c>
+      <c r="G21">
+        <v>0</v>
+      </c>
+      <c r="I21" t="s">
+        <v>42</v>
+      </c>
+      <c r="J21">
+        <v>0</v>
+      </c>
+      <c r="K21">
+        <v>1</v>
+      </c>
+      <c r="L21" t="s">
+        <v>57</v>
+      </c>
+      <c r="M21">
+        <v>0</v>
+      </c>
+      <c r="N21" t="s">
+        <v>86</v>
+      </c>
+      <c r="O21">
+        <v>0.2</v>
+      </c>
+      <c r="P21" t="s">
+        <v>89</v>
+      </c>
+      <c r="Q21">
+        <v>-0.05</v>
+      </c>
+    </row>
+    <row r="22" spans="2:17" x14ac:dyDescent="0.25">
+      <c r="B22">
+        <v>2015</v>
+      </c>
+      <c r="C22" t="s">
+        <v>90</v>
+      </c>
+      <c r="D22" t="s">
+        <v>91</v>
+      </c>
+      <c r="E22">
+        <v>1000</v>
+      </c>
+      <c r="F22" t="s">
+        <v>34</v>
+      </c>
+      <c r="G22">
+        <v>0</v>
+      </c>
+      <c r="I22" t="s">
+        <v>42</v>
+      </c>
+      <c r="J22">
+        <v>0</v>
+      </c>
+      <c r="K22">
+        <v>1</v>
+      </c>
+      <c r="L22" t="s">
+        <v>57</v>
+      </c>
+      <c r="M22">
+        <v>0</v>
+      </c>
+      <c r="N22" t="s">
+        <v>86</v>
+      </c>
+      <c r="O22">
+        <v>0.3</v>
+      </c>
+      <c r="P22" t="s">
+        <v>89</v>
+      </c>
+      <c r="Q22">
+        <v>-0.1</v>
+      </c>
+    </row>
+    <row r="23" spans="2:17" x14ac:dyDescent="0.25">
+      <c r="B23">
+        <v>2016</v>
+      </c>
+      <c r="C23" t="s">
+        <v>92</v>
+      </c>
+      <c r="D23" t="s">
+        <v>93</v>
+      </c>
+      <c r="E23">
+        <v>1000</v>
+      </c>
+      <c r="F23" t="s">
+        <v>34</v>
+      </c>
+      <c r="G23">
+        <v>0</v>
+      </c>
+      <c r="I23" t="s">
+        <v>42</v>
+      </c>
+      <c r="J23">
+        <v>0</v>
+      </c>
+      <c r="K23">
+        <v>1</v>
+      </c>
+      <c r="L23" t="s">
+        <v>57</v>
+      </c>
+      <c r="M23">
+        <v>0</v>
+      </c>
+      <c r="N23" t="s">
+        <v>94</v>
+      </c>
+      <c r="O23">
+        <v>0.08</v>
+      </c>
+      <c r="Q23">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="24" spans="2:17" x14ac:dyDescent="0.25">
+      <c r="B24">
+        <v>2017</v>
+      </c>
+      <c r="C24" t="s">
+        <v>95</v>
+      </c>
+      <c r="D24" t="s">
+        <v>96</v>
+      </c>
+      <c r="E24">
+        <v>1000</v>
+      </c>
+      <c r="F24" t="s">
+        <v>34</v>
+      </c>
+      <c r="G24">
+        <v>0</v>
+      </c>
+      <c r="I24" t="s">
+        <v>42</v>
+      </c>
+      <c r="J24">
+        <v>0</v>
+      </c>
+      <c r="K24">
+        <v>1</v>
+      </c>
+      <c r="L24" t="s">
+        <v>57</v>
+      </c>
+      <c r="M24">
+        <v>0</v>
+      </c>
+      <c r="N24" t="s">
+        <v>94</v>
+      </c>
+      <c r="O24">
+        <v>0.16</v>
+      </c>
+      <c r="Q24">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="25" spans="2:17" x14ac:dyDescent="0.25">
+      <c r="B25">
+        <v>2018</v>
+      </c>
+      <c r="C25" t="s">
+        <v>97</v>
+      </c>
+      <c r="D25" t="s">
+        <v>98</v>
+      </c>
+      <c r="E25">
+        <v>1000</v>
+      </c>
+      <c r="F25" t="s">
+        <v>34</v>
+      </c>
+      <c r="G25">
+        <v>0</v>
+      </c>
+      <c r="I25" t="s">
+        <v>42</v>
+      </c>
+      <c r="J25">
+        <v>0</v>
+      </c>
+      <c r="K25">
+        <v>1</v>
+      </c>
+      <c r="L25" t="s">
+        <v>57</v>
+      </c>
+      <c r="M25">
+        <v>0</v>
+      </c>
+      <c r="N25" t="s">
+        <v>94</v>
+      </c>
+      <c r="O25">
+        <v>0.28000000000000003</v>
+      </c>
+      <c r="Q25">
+        <v>0</v>
       </c>
     </row>
   </sheetData>
